--- a/ExcelRAddIn/Tests/Descriptive Statistics.xlsx
+++ b/ExcelRAddIn/Tests/Descriptive Statistics.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Development\Projects\C#\Office\ExcelRAddIn\Tests\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Development\Projects\C#\Office\Office365 AddIns\ExcelRAddIn\Tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84530EFD-059D-40A4-8891-C7076FCFC5D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{671946CB-F6DF-478D-9FB1-25C3A547E44A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{5003AA1E-52FB-411B-9B31-43F0075F6D84}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{5003AA1E-52FB-411B-9B31-43F0075F6D84}"/>
   </bookViews>
   <sheets>
     <sheet name="References" sheetId="1" r:id="rId1"/>
@@ -308,9 +308,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -348,7 +348,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -454,7 +454,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -596,7 +596,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -625,826 +625,118 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9F63317-D946-4322-9CB8-4E6BA5495368}">
-  <dimension ref="B2:AA13"/>
+  <dimension ref="B2:D13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="19" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>0</v>
       </c>
       <c r="D2" t="str" cm="1">
-        <f t="array" ref="D2:T2">TRANSPOSE(_xll.RScript.Evaluate(B2))</f>
-        <v>lubridate</v>
-      </c>
-      <c r="E2" t="str">
-        <v>forcats</v>
-      </c>
-      <c r="F2" t="str">
-        <v>stringr</v>
-      </c>
-      <c r="G2" t="str">
-        <v>dplyr</v>
-      </c>
-      <c r="H2" t="str">
-        <v>purrr</v>
-      </c>
-      <c r="I2" t="str">
-        <v>readr</v>
-      </c>
-      <c r="J2" t="str">
-        <v>tidyr</v>
-      </c>
-      <c r="K2" t="str">
-        <v>tibble</v>
-      </c>
-      <c r="L2" t="str">
-        <v>ggplot2</v>
-      </c>
-      <c r="M2" t="str">
-        <v>tidyverse</v>
-      </c>
-      <c r="N2" t="str">
-        <v>stats</v>
-      </c>
-      <c r="O2" t="str">
-        <v>graphics</v>
-      </c>
-      <c r="P2" t="str">
-        <v>grDevices</v>
-      </c>
-      <c r="Q2" t="str">
-        <v>utils</v>
-      </c>
-      <c r="R2" t="str">
-        <v>datasets</v>
-      </c>
-      <c r="S2" t="str">
-        <v>methods</v>
-      </c>
-      <c r="T2" t="str">
-        <v>base</v>
-      </c>
-    </row>
-    <row r="3" spans="2:27" x14ac:dyDescent="0.3">
+        <f t="array" ref="D2">TRANSPOSE(_xll.RScript.Evaluate(B2, TRUE))</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="3" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>4</v>
       </c>
       <c r="D3" t="str" cm="1">
-        <f t="array" ref="D3:AA3">TRANSPOSE(_xll.RScript.Evaluate(B3))</f>
-        <v>tsibble</v>
-      </c>
-      <c r="E3" t="str">
-        <v>StatsR</v>
-      </c>
-      <c r="F3" t="str">
-        <v>moments</v>
-      </c>
-      <c r="G3" t="str">
-        <v>summarytools</v>
-      </c>
-      <c r="H3" t="str">
-        <v>formattable</v>
-      </c>
-      <c r="I3" t="str">
-        <v>plotly</v>
-      </c>
-      <c r="J3" t="str">
-        <v>ggpubr</v>
-      </c>
-      <c r="K3" t="str">
-        <v>lubridate</v>
-      </c>
-      <c r="L3" t="str">
-        <v>forcats</v>
-      </c>
-      <c r="M3" t="str">
-        <v>stringr</v>
-      </c>
-      <c r="N3" t="str">
-        <v>dplyr</v>
-      </c>
-      <c r="O3" t="str">
-        <v>purrr</v>
-      </c>
-      <c r="P3" t="str">
-        <v>readr</v>
-      </c>
-      <c r="Q3" t="str">
-        <v>tidyr</v>
-      </c>
-      <c r="R3" t="str">
-        <v>tibble</v>
-      </c>
-      <c r="S3" t="str">
-        <v>ggplot2</v>
-      </c>
-      <c r="T3" t="str">
-        <v>tidyverse</v>
-      </c>
-      <c r="U3" t="str">
-        <v>stats</v>
-      </c>
-      <c r="V3" t="str">
-        <v>graphics</v>
-      </c>
-      <c r="W3" t="str">
-        <v>grDevices</v>
-      </c>
-      <c r="X3" t="str">
-        <v>utils</v>
-      </c>
-      <c r="Y3" t="str">
-        <v>datasets</v>
-      </c>
-      <c r="Z3" t="str">
-        <v>methods</v>
-      </c>
-      <c r="AA3" t="str">
-        <v>base</v>
-      </c>
-    </row>
-    <row r="4" spans="2:27" x14ac:dyDescent="0.3">
+        <f t="array" ref="D3">TRANSPOSE(_xll.RScript.Evaluate(B3, TRUE))</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>5</v>
       </c>
       <c r="D4" t="str" cm="1">
-        <f t="array" ref="D4:T4">TRANSPOSE(_xll.RScript.Evaluate(B4))</f>
-        <v>lubridate</v>
-      </c>
-      <c r="E4" t="str">
-        <v>forcats</v>
-      </c>
-      <c r="F4" t="str">
-        <v>stringr</v>
-      </c>
-      <c r="G4" t="str">
-        <v>dplyr</v>
-      </c>
-      <c r="H4" t="str">
-        <v>purrr</v>
-      </c>
-      <c r="I4" t="str">
-        <v>readr</v>
-      </c>
-      <c r="J4" t="str">
-        <v>tidyr</v>
-      </c>
-      <c r="K4" t="str">
-        <v>tibble</v>
-      </c>
-      <c r="L4" t="str">
-        <v>ggplot2</v>
-      </c>
-      <c r="M4" t="str">
-        <v>tidyverse</v>
-      </c>
-      <c r="N4" t="str">
-        <v>stats</v>
-      </c>
-      <c r="O4" t="str">
-        <v>graphics</v>
-      </c>
-      <c r="P4" t="str">
-        <v>grDevices</v>
-      </c>
-      <c r="Q4" t="str">
-        <v>utils</v>
-      </c>
-      <c r="R4" t="str">
-        <v>datasets</v>
-      </c>
-      <c r="S4" t="str">
-        <v>methods</v>
-      </c>
-      <c r="T4" t="str">
-        <v>base</v>
-      </c>
-    </row>
-    <row r="5" spans="2:27" x14ac:dyDescent="0.3">
+        <f t="array" ref="D4">TRANSPOSE(_xll.RScript.Evaluate(B4, TRUE))</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>6</v>
       </c>
       <c r="D5" t="str" cm="1">
-        <f t="array" ref="D5:AA5">TRANSPOSE(_xll.RScript.Evaluate(B5))</f>
-        <v>tsibble</v>
-      </c>
-      <c r="E5" t="str">
-        <v>StatsR</v>
-      </c>
-      <c r="F5" t="str">
-        <v>moments</v>
-      </c>
-      <c r="G5" t="str">
-        <v>summarytools</v>
-      </c>
-      <c r="H5" t="str">
-        <v>formattable</v>
-      </c>
-      <c r="I5" t="str">
-        <v>plotly</v>
-      </c>
-      <c r="J5" t="str">
-        <v>ggpubr</v>
-      </c>
-      <c r="K5" t="str">
-        <v>lubridate</v>
-      </c>
-      <c r="L5" t="str">
-        <v>forcats</v>
-      </c>
-      <c r="M5" t="str">
-        <v>stringr</v>
-      </c>
-      <c r="N5" t="str">
-        <v>dplyr</v>
-      </c>
-      <c r="O5" t="str">
-        <v>purrr</v>
-      </c>
-      <c r="P5" t="str">
-        <v>readr</v>
-      </c>
-      <c r="Q5" t="str">
-        <v>tidyr</v>
-      </c>
-      <c r="R5" t="str">
-        <v>tibble</v>
-      </c>
-      <c r="S5" t="str">
-        <v>ggplot2</v>
-      </c>
-      <c r="T5" t="str">
-        <v>tidyverse</v>
-      </c>
-      <c r="U5" t="str">
-        <v>stats</v>
-      </c>
-      <c r="V5" t="str">
-        <v>graphics</v>
-      </c>
-      <c r="W5" t="str">
-        <v>grDevices</v>
-      </c>
-      <c r="X5" t="str">
-        <v>utils</v>
-      </c>
-      <c r="Y5" t="str">
-        <v>datasets</v>
-      </c>
-      <c r="Z5" t="str">
-        <v>methods</v>
-      </c>
-      <c r="AA5" t="str">
-        <v>base</v>
-      </c>
-    </row>
-    <row r="6" spans="2:27" x14ac:dyDescent="0.3">
+        <f t="array" ref="D5">TRANSPOSE(_xll.RScript.Evaluate(B5, TRUE))</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>7</v>
       </c>
       <c r="D6" t="str" cm="1">
-        <f t="array" ref="D6:U6">TRANSPOSE(_xll.RScript.Evaluate(B6))</f>
-        <v>ggpubr</v>
-      </c>
-      <c r="E6" t="str">
-        <v>lubridate</v>
-      </c>
-      <c r="F6" t="str">
-        <v>forcats</v>
-      </c>
-      <c r="G6" t="str">
-        <v>stringr</v>
-      </c>
-      <c r="H6" t="str">
-        <v>dplyr</v>
-      </c>
-      <c r="I6" t="str">
-        <v>purrr</v>
-      </c>
-      <c r="J6" t="str">
-        <v>readr</v>
-      </c>
-      <c r="K6" t="str">
-        <v>tidyr</v>
-      </c>
-      <c r="L6" t="str">
-        <v>tibble</v>
-      </c>
-      <c r="M6" t="str">
-        <v>ggplot2</v>
-      </c>
-      <c r="N6" t="str">
-        <v>tidyverse</v>
-      </c>
-      <c r="O6" t="str">
-        <v>stats</v>
-      </c>
-      <c r="P6" t="str">
-        <v>graphics</v>
-      </c>
-      <c r="Q6" t="str">
-        <v>grDevices</v>
-      </c>
-      <c r="R6" t="str">
-        <v>utils</v>
-      </c>
-      <c r="S6" t="str">
-        <v>datasets</v>
-      </c>
-      <c r="T6" t="str">
-        <v>methods</v>
-      </c>
-      <c r="U6" t="str">
-        <v>base</v>
-      </c>
-    </row>
-    <row r="7" spans="2:27" x14ac:dyDescent="0.3">
+        <f t="array" ref="D6">TRANSPOSE(_xll.RScript.Evaluate(B6, TRUE))</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>8</v>
       </c>
       <c r="D7" t="str" cm="1">
-        <f t="array" ref="D7:V7">TRANSPOSE(_xll.RScript.Evaluate(B7))</f>
-        <v>plotly</v>
-      </c>
-      <c r="E7" t="str">
-        <v>ggpubr</v>
-      </c>
-      <c r="F7" t="str">
-        <v>lubridate</v>
-      </c>
-      <c r="G7" t="str">
-        <v>forcats</v>
-      </c>
-      <c r="H7" t="str">
-        <v>stringr</v>
-      </c>
-      <c r="I7" t="str">
-        <v>dplyr</v>
-      </c>
-      <c r="J7" t="str">
-        <v>purrr</v>
-      </c>
-      <c r="K7" t="str">
-        <v>readr</v>
-      </c>
-      <c r="L7" t="str">
-        <v>tidyr</v>
-      </c>
-      <c r="M7" t="str">
-        <v>tibble</v>
-      </c>
-      <c r="N7" t="str">
-        <v>ggplot2</v>
-      </c>
-      <c r="O7" t="str">
-        <v>tidyverse</v>
-      </c>
-      <c r="P7" t="str">
-        <v>stats</v>
-      </c>
-      <c r="Q7" t="str">
-        <v>graphics</v>
-      </c>
-      <c r="R7" t="str">
-        <v>grDevices</v>
-      </c>
-      <c r="S7" t="str">
-        <v>utils</v>
-      </c>
-      <c r="T7" t="str">
-        <v>datasets</v>
-      </c>
-      <c r="U7" t="str">
-        <v>methods</v>
-      </c>
-      <c r="V7" t="str">
-        <v>base</v>
-      </c>
-    </row>
-    <row r="8" spans="2:27" x14ac:dyDescent="0.3">
+        <f t="array" ref="D7">TRANSPOSE(_xll.RScript.Evaluate(B7, TRUE))</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>9</v>
       </c>
       <c r="D8" t="str" cm="1">
-        <f t="array" ref="D8:V8">TRANSPOSE(_xll.RScript.Evaluate(B8))</f>
-        <v>plotly</v>
-      </c>
-      <c r="E8" t="str">
-        <v>ggpubr</v>
-      </c>
-      <c r="F8" t="str">
-        <v>lubridate</v>
-      </c>
-      <c r="G8" t="str">
-        <v>forcats</v>
-      </c>
-      <c r="H8" t="str">
-        <v>stringr</v>
-      </c>
-      <c r="I8" t="str">
-        <v>dplyr</v>
-      </c>
-      <c r="J8" t="str">
-        <v>purrr</v>
-      </c>
-      <c r="K8" t="str">
-        <v>readr</v>
-      </c>
-      <c r="L8" t="str">
-        <v>tidyr</v>
-      </c>
-      <c r="M8" t="str">
-        <v>tibble</v>
-      </c>
-      <c r="N8" t="str">
-        <v>ggplot2</v>
-      </c>
-      <c r="O8" t="str">
-        <v>tidyverse</v>
-      </c>
-      <c r="P8" t="str">
-        <v>stats</v>
-      </c>
-      <c r="Q8" t="str">
-        <v>graphics</v>
-      </c>
-      <c r="R8" t="str">
-        <v>grDevices</v>
-      </c>
-      <c r="S8" t="str">
-        <v>utils</v>
-      </c>
-      <c r="T8" t="str">
-        <v>datasets</v>
-      </c>
-      <c r="U8" t="str">
-        <v>methods</v>
-      </c>
-      <c r="V8" t="str">
-        <v>base</v>
-      </c>
-    </row>
-    <row r="9" spans="2:27" x14ac:dyDescent="0.3">
+        <f t="array" ref="D8">TRANSPOSE(_xll.RScript.Evaluate(B8, TRUE))</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>10</v>
       </c>
       <c r="D9" t="str" cm="1">
-        <f t="array" ref="D9:W9">TRANSPOSE(_xll.RScript.Evaluate(B9))</f>
-        <v>formattable</v>
-      </c>
-      <c r="E9" t="str">
-        <v>plotly</v>
-      </c>
-      <c r="F9" t="str">
-        <v>ggpubr</v>
-      </c>
-      <c r="G9" t="str">
-        <v>lubridate</v>
-      </c>
-      <c r="H9" t="str">
-        <v>forcats</v>
-      </c>
-      <c r="I9" t="str">
-        <v>stringr</v>
-      </c>
-      <c r="J9" t="str">
-        <v>dplyr</v>
-      </c>
-      <c r="K9" t="str">
-        <v>purrr</v>
-      </c>
-      <c r="L9" t="str">
-        <v>readr</v>
-      </c>
-      <c r="M9" t="str">
-        <v>tidyr</v>
-      </c>
-      <c r="N9" t="str">
-        <v>tibble</v>
-      </c>
-      <c r="O9" t="str">
-        <v>ggplot2</v>
-      </c>
-      <c r="P9" t="str">
-        <v>tidyverse</v>
-      </c>
-      <c r="Q9" t="str">
-        <v>stats</v>
-      </c>
-      <c r="R9" t="str">
-        <v>graphics</v>
-      </c>
-      <c r="S9" t="str">
-        <v>grDevices</v>
-      </c>
-      <c r="T9" t="str">
-        <v>utils</v>
-      </c>
-      <c r="U9" t="str">
-        <v>datasets</v>
-      </c>
-      <c r="V9" t="str">
-        <v>methods</v>
-      </c>
-      <c r="W9" t="str">
-        <v>base</v>
-      </c>
-    </row>
-    <row r="10" spans="2:27" x14ac:dyDescent="0.3">
+        <f t="array" ref="D9">TRANSPOSE(_xll.RScript.Evaluate(B9, TRUE))</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>11</v>
       </c>
       <c r="D10" t="str" cm="1">
-        <f t="array" ref="D10:X10">TRANSPOSE(_xll.RScript.Evaluate(B10))</f>
-        <v>summarytools</v>
-      </c>
-      <c r="E10" t="str">
-        <v>formattable</v>
-      </c>
-      <c r="F10" t="str">
-        <v>plotly</v>
-      </c>
-      <c r="G10" t="str">
-        <v>ggpubr</v>
-      </c>
-      <c r="H10" t="str">
-        <v>lubridate</v>
-      </c>
-      <c r="I10" t="str">
-        <v>forcats</v>
-      </c>
-      <c r="J10" t="str">
-        <v>stringr</v>
-      </c>
-      <c r="K10" t="str">
-        <v>dplyr</v>
-      </c>
-      <c r="L10" t="str">
-        <v>purrr</v>
-      </c>
-      <c r="M10" t="str">
-        <v>readr</v>
-      </c>
-      <c r="N10" t="str">
-        <v>tidyr</v>
-      </c>
-      <c r="O10" t="str">
-        <v>tibble</v>
-      </c>
-      <c r="P10" t="str">
-        <v>ggplot2</v>
-      </c>
-      <c r="Q10" t="str">
-        <v>tidyverse</v>
-      </c>
-      <c r="R10" t="str">
-        <v>stats</v>
-      </c>
-      <c r="S10" t="str">
-        <v>graphics</v>
-      </c>
-      <c r="T10" t="str">
-        <v>grDevices</v>
-      </c>
-      <c r="U10" t="str">
-        <v>utils</v>
-      </c>
-      <c r="V10" t="str">
-        <v>datasets</v>
-      </c>
-      <c r="W10" t="str">
-        <v>methods</v>
-      </c>
-      <c r="X10" t="str">
-        <v>base</v>
-      </c>
-    </row>
-    <row r="11" spans="2:27" x14ac:dyDescent="0.3">
+        <f t="array" ref="D10">TRANSPOSE(_xll.RScript.Evaluate(B10, TRUE))</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="11" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>12</v>
       </c>
       <c r="D11" t="str" cm="1">
-        <f t="array" ref="D11:Y11">TRANSPOSE(_xll.RScript.Evaluate(B11))</f>
-        <v>moments</v>
-      </c>
-      <c r="E11" t="str">
-        <v>summarytools</v>
-      </c>
-      <c r="F11" t="str">
-        <v>formattable</v>
-      </c>
-      <c r="G11" t="str">
-        <v>plotly</v>
-      </c>
-      <c r="H11" t="str">
-        <v>ggpubr</v>
-      </c>
-      <c r="I11" t="str">
-        <v>lubridate</v>
-      </c>
-      <c r="J11" t="str">
-        <v>forcats</v>
-      </c>
-      <c r="K11" t="str">
-        <v>stringr</v>
-      </c>
-      <c r="L11" t="str">
-        <v>dplyr</v>
-      </c>
-      <c r="M11" t="str">
-        <v>purrr</v>
-      </c>
-      <c r="N11" t="str">
-        <v>readr</v>
-      </c>
-      <c r="O11" t="str">
-        <v>tidyr</v>
-      </c>
-      <c r="P11" t="str">
-        <v>tibble</v>
-      </c>
-      <c r="Q11" t="str">
-        <v>ggplot2</v>
-      </c>
-      <c r="R11" t="str">
-        <v>tidyverse</v>
-      </c>
-      <c r="S11" t="str">
-        <v>stats</v>
-      </c>
-      <c r="T11" t="str">
-        <v>graphics</v>
-      </c>
-      <c r="U11" t="str">
-        <v>grDevices</v>
-      </c>
-      <c r="V11" t="str">
-        <v>utils</v>
-      </c>
-      <c r="W11" t="str">
-        <v>datasets</v>
-      </c>
-      <c r="X11" t="str">
-        <v>methods</v>
-      </c>
-      <c r="Y11" t="str">
-        <v>base</v>
-      </c>
-    </row>
-    <row r="12" spans="2:27" x14ac:dyDescent="0.3">
+        <f t="array" ref="D11">TRANSPOSE(_xll.RScript.Evaluate(B11, TRUE))</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="12" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>13</v>
       </c>
       <c r="D12" t="str" cm="1">
-        <f t="array" ref="D12:Z12">TRANSPOSE(_xll.RScript.Evaluate(B12))</f>
-        <v>StatsR</v>
-      </c>
-      <c r="E12" t="str">
-        <v>moments</v>
-      </c>
-      <c r="F12" t="str">
-        <v>summarytools</v>
-      </c>
-      <c r="G12" t="str">
-        <v>formattable</v>
-      </c>
-      <c r="H12" t="str">
-        <v>plotly</v>
-      </c>
-      <c r="I12" t="str">
-        <v>ggpubr</v>
-      </c>
-      <c r="J12" t="str">
-        <v>lubridate</v>
-      </c>
-      <c r="K12" t="str">
-        <v>forcats</v>
-      </c>
-      <c r="L12" t="str">
-        <v>stringr</v>
-      </c>
-      <c r="M12" t="str">
-        <v>dplyr</v>
-      </c>
-      <c r="N12" t="str">
-        <v>purrr</v>
-      </c>
-      <c r="O12" t="str">
-        <v>readr</v>
-      </c>
-      <c r="P12" t="str">
-        <v>tidyr</v>
-      </c>
-      <c r="Q12" t="str">
-        <v>tibble</v>
-      </c>
-      <c r="R12" t="str">
-        <v>ggplot2</v>
-      </c>
-      <c r="S12" t="str">
-        <v>tidyverse</v>
-      </c>
-      <c r="T12" t="str">
-        <v>stats</v>
-      </c>
-      <c r="U12" t="str">
-        <v>graphics</v>
-      </c>
-      <c r="V12" t="str">
-        <v>grDevices</v>
-      </c>
-      <c r="W12" t="str">
-        <v>utils</v>
-      </c>
-      <c r="X12" t="str">
-        <v>datasets</v>
-      </c>
-      <c r="Y12" t="str">
-        <v>methods</v>
-      </c>
-      <c r="Z12" t="str">
-        <v>base</v>
-      </c>
-    </row>
-    <row r="13" spans="2:27" x14ac:dyDescent="0.3">
+        <f t="array" ref="D12">TRANSPOSE(_xll.RScript.Evaluate(B12, TRUE))</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="13" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
         <v>1</v>
       </c>
       <c r="D13" t="str" cm="1">
-        <f t="array" ref="D13:AA13">TRANSPOSE(_xll.RScript.Evaluate(B13))</f>
-        <v>tsibble</v>
-      </c>
-      <c r="E13" t="str">
-        <v>StatsR</v>
-      </c>
-      <c r="F13" t="str">
-        <v>moments</v>
-      </c>
-      <c r="G13" t="str">
-        <v>summarytools</v>
-      </c>
-      <c r="H13" t="str">
-        <v>formattable</v>
-      </c>
-      <c r="I13" t="str">
-        <v>plotly</v>
-      </c>
-      <c r="J13" t="str">
-        <v>ggpubr</v>
-      </c>
-      <c r="K13" t="str">
-        <v>lubridate</v>
-      </c>
-      <c r="L13" t="str">
-        <v>forcats</v>
-      </c>
-      <c r="M13" t="str">
-        <v>stringr</v>
-      </c>
-      <c r="N13" t="str">
-        <v>dplyr</v>
-      </c>
-      <c r="O13" t="str">
-        <v>purrr</v>
-      </c>
-      <c r="P13" t="str">
-        <v>readr</v>
-      </c>
-      <c r="Q13" t="str">
-        <v>tidyr</v>
-      </c>
-      <c r="R13" t="str">
-        <v>tibble</v>
-      </c>
-      <c r="S13" t="str">
-        <v>ggplot2</v>
-      </c>
-      <c r="T13" t="str">
-        <v>tidyverse</v>
-      </c>
-      <c r="U13" t="str">
-        <v>stats</v>
-      </c>
-      <c r="V13" t="str">
-        <v>graphics</v>
-      </c>
-      <c r="W13" t="str">
-        <v>grDevices</v>
-      </c>
-      <c r="X13" t="str">
-        <v>utils</v>
-      </c>
-      <c r="Y13" t="str">
-        <v>datasets</v>
-      </c>
-      <c r="Z13" t="str">
-        <v>methods</v>
-      </c>
-      <c r="AA13" t="str">
-        <v>base</v>
+        <f t="array" ref="D13">TRANSPOSE(_xll.RScript.Evaluate(B13, TRUE))</f>
+        <v>OK</v>
       </c>
     </row>
   </sheetData>
@@ -1847,7 +1139,7 @@
       </c>
       <c r="C2" t="str" cm="1">
         <f t="array" ref="C2">_xll.RScript.Evaluate(B2)</f>
-        <v>D:/Development/Projects/C#/Office/ExcelRAddIn/ExcelRAddIn/bin/Debug</v>
+        <v>D:/Development/Projects/C#/Office/Office365 AddIns/ExcelRAddIn/ExcelRAddIn/bin/Debug</v>
       </c>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
